--- a/03_outputs/03.5_rmse_test_loocv.xlsx
+++ b/03_outputs/03.5_rmse_test_loocv.xlsx
@@ -1,15 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniandes-my.sharepoint.com/personal/mh_torres_uniandes_edu_co/Documents/Pregrado/8vo Semestre/01_Big_Data/03_Talleres/taller_1_grupo_05/03_outputs/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_20CE4016F78BC1F1873D982E1A2E597415B23BF3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA1A34DC-DAB9-42B8-994E-175630D72163}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -19,9 +38,6 @@
     <t>modelo</t>
   </si>
   <si>
-    <t>complejidad</t>
-  </si>
-  <si>
     <t>RMSE_train</t>
   </si>
   <si>
@@ -31,18 +47,6 @@
     <t>loocv</t>
   </si>
   <si>
-    <t>M1.1</t>
-  </si>
-  <si>
-    <t>M1.2</t>
-  </si>
-  <si>
-    <t>M2.1</t>
-  </si>
-  <si>
-    <t>M2.2</t>
-  </si>
-  <si>
     <t>MA1</t>
   </si>
   <si>
@@ -101,13 +105,32 @@
   </si>
   <si>
     <t>MA20</t>
+  </si>
+  <si>
+    <t>Numero Parametros</t>
+  </si>
+  <si>
+    <t>Edad Incondicional</t>
+  </si>
+  <si>
+    <t>Edad Condicional</t>
+  </si>
+  <si>
+    <t>Genero Incondicional</t>
+  </si>
+  <si>
+    <t>Genero Condicional</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,13 +146,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -141,27 +177,40 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -199,7 +248,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -233,6 +282,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -267,9 +317,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -442,432 +493,437 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" customWidth="1"/>
+    <col min="3" max="3" width="17.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B2">
         <v>3</v>
       </c>
-      <c r="C2">
-        <v>0.8656665590364609</v>
-      </c>
-      <c r="D2">
-        <v>0.8918339593794845</v>
-      </c>
-      <c r="E2">
-        <v>0.8660059070635633</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="C2" s="2">
+        <v>0.86566655903646095</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.89183395937948451</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.86600590706356328</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="B3">
         <v>5</v>
       </c>
-      <c r="C3">
-        <v>0.8150655005288985</v>
-      </c>
-      <c r="D3">
-        <v>0.8443006955475558</v>
-      </c>
-      <c r="E3">
-        <v>0.8156088837376079</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="C3" s="2">
+        <v>0.81506550052889848</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.84430069554755582</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.81560888373760787</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
-      <c r="C4">
-        <v>0.8804997184028066</v>
-      </c>
-      <c r="D4">
-        <v>0.9065203498553729</v>
-      </c>
-      <c r="E4">
-        <v>0.8806731720023663</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="C4" s="2">
+        <v>0.88049971840280661</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.90652034985537289</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0.88067317200236628</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B5">
         <v>13</v>
       </c>
-      <c r="C5">
-        <v>0.695298653558433</v>
-      </c>
-      <c r="D5">
-        <v>0.71523380932507</v>
-      </c>
-      <c r="E5">
-        <v>0.6963337447067915</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="C5" s="2">
+        <v>0.69529865355843301</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.71523380932506997</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.69633374470679155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B6">
         <v>7</v>
       </c>
-      <c r="C6">
-        <v>0.7552780464262018</v>
-      </c>
-      <c r="D6">
-        <v>0.770238137426498</v>
-      </c>
-      <c r="E6">
-        <v>0.7558846225356916</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="C6" s="2">
+        <v>0.75527804642620178</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.77023813742649805</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.75588462253569155</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B7">
         <v>7</v>
       </c>
-      <c r="C7">
-        <v>0.6371539793224804</v>
-      </c>
-      <c r="D7">
-        <v>0.6683054851449733</v>
-      </c>
-      <c r="E7">
-        <v>0.6377334455613253</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="C7" s="2">
+        <v>0.63715397932248041</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.66830548514497334</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.63773344556132527</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B8">
         <v>14</v>
       </c>
-      <c r="C8">
-        <v>0.5939354978657462</v>
-      </c>
-      <c r="D8">
-        <v>0.6346762715990099</v>
-      </c>
-      <c r="E8">
-        <v>0.5949427290348189</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="C8" s="2">
+        <v>0.59393549786574618</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.63467627159900986</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.59494272903481893</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B9">
         <v>7</v>
       </c>
-      <c r="C9">
-        <v>0.6744104825730918</v>
-      </c>
-      <c r="D9">
-        <v>0.6893097244672595</v>
-      </c>
-      <c r="E9">
-        <v>0.6749993118643008</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="C9" s="2">
+        <v>0.67441048257309177</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0.68930972446725947</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.67499931186430084</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B10">
         <v>16</v>
       </c>
-      <c r="C10">
-        <v>0.6500693755426339</v>
-      </c>
-      <c r="D10">
+      <c r="C10" s="2">
+        <v>0.65006937554263389</v>
+      </c>
+      <c r="D10" s="2">
         <v>0.6721469678859241</v>
       </c>
-      <c r="E10">
-        <v>0.6512556740322311</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="E10" s="2">
+        <v>0.65125567403223106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B11">
         <v>9</v>
       </c>
-      <c r="C11">
-        <v>0.6804207171357721</v>
-      </c>
-      <c r="D11">
+      <c r="C11" s="2">
+        <v>0.68042071713577212</v>
+      </c>
+      <c r="D11" s="2">
         <v>0.6909742254038499</v>
       </c>
-      <c r="E11">
-        <v>0.6811491407028549</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="E11" s="2">
+        <v>0.68114914070285493</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B12">
         <v>6</v>
       </c>
-      <c r="C12">
-        <v>0.6937312421885157</v>
-      </c>
-      <c r="D12">
-        <v>0.7148658421551138</v>
-      </c>
-      <c r="E12">
-        <v>0.6942480089309135</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="C12" s="2">
+        <v>0.69373124218851567</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.71486584215511384</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.69424800893091354</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B13">
         <v>13</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <v>0.659527406388426</v>
       </c>
-      <c r="D13">
-        <v>0.6761529924733254</v>
-      </c>
-      <c r="E13">
-        <v>0.660498045755036</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="D13" s="2">
+        <v>0.67615299247332539</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.66049804575503601</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <v>13</v>
       </c>
-      <c r="C14">
-        <v>0.6145030613455588</v>
-      </c>
-      <c r="D14">
-        <v>0.6493984781900994</v>
-      </c>
-      <c r="E14">
-        <v>0.6154109024225654</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="C14" s="2">
+        <v>0.61450306134555877</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0.64939847819009944</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0.61541090242256535</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B15">
         <v>13</v>
       </c>
-      <c r="C15">
-        <v>0.6061499187518795</v>
-      </c>
-      <c r="D15">
-        <v>0.6365089292949198</v>
-      </c>
-      <c r="E15">
-        <v>0.6071080590834746</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="C15" s="2">
+        <v>0.60614991875187951</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0.63650892929491976</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0.60710805908347465</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B16">
         <v>10</v>
       </c>
-      <c r="C16">
-        <v>0.6414474867116047</v>
-      </c>
-      <c r="D16">
-        <v>0.6734557348869212</v>
-      </c>
-      <c r="E16">
+      <c r="C16" s="2">
+        <v>0.64144748671160468</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0.67345573488692123</v>
+      </c>
+      <c r="E16" s="2">
         <v>0.6422228186414316</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B17">
         <v>14</v>
       </c>
-      <c r="C17">
-        <v>0.635018099645731</v>
-      </c>
-      <c r="D17">
-        <v>0.6663814451051369</v>
-      </c>
-      <c r="E17">
-        <v>0.6361835634656033</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="C17" s="2">
+        <v>0.63501809964573097</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0.66638144510513686</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0.63618356346560334</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B18">
         <v>12</v>
       </c>
-      <c r="C18">
-        <v>0.5853174121555667</v>
-      </c>
-      <c r="D18">
-        <v>0.6220646286148487</v>
-      </c>
-      <c r="E18">
-        <v>0.5862095746351895</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="C18" s="2">
+        <v>0.58531741215556665</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0.62206462861484868</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0.58620957463518952</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B19">
         <v>11</v>
       </c>
-      <c r="C19">
-        <v>0.5908286129387931</v>
-      </c>
-      <c r="D19">
-        <v>0.6292832352784559</v>
-      </c>
-      <c r="E19">
-        <v>0.5917376515684558</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20">
+      <c r="C19" s="2">
+        <v>0.59082861293879307</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0.62928323527845587</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0.59173765156845581</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3">
         <v>14</v>
       </c>
-      <c r="C20">
-        <v>0.5723088891963036</v>
-      </c>
-      <c r="D20">
-        <v>0.608060171061505</v>
-      </c>
-      <c r="E20">
-        <v>0.5733750110375478</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="C20" s="4">
+        <v>0.57230888919630363</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0.60806017106150501</v>
+      </c>
+      <c r="E20" s="4">
+        <v>0.57337501103754784</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B21">
         <v>27</v>
       </c>
-      <c r="C21">
-        <v>0.6051934572893271</v>
-      </c>
-      <c r="D21">
+      <c r="C21" s="2">
+        <v>0.60519345728932705</v>
+      </c>
+      <c r="D21" s="2">
         <v>0.6351218513440603</v>
       </c>
-      <c r="E21">
-        <v>0.6072906579816894</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="E21" s="2">
+        <v>0.60729065798168935</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B22">
         <v>16</v>
       </c>
-      <c r="C22">
-        <v>0.6076937856622779</v>
-      </c>
-      <c r="D22">
-        <v>0.6380434083438097</v>
-      </c>
-      <c r="E22">
-        <v>0.6088637734135117</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23">
+      <c r="C22" s="2">
+        <v>0.60769378566227794</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0.63804340834380968</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0.60886377341351172</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3">
         <v>15</v>
       </c>
-      <c r="C23">
-        <v>0.5721064212391598</v>
-      </c>
-      <c r="D23">
-        <v>0.607206296989876</v>
-      </c>
-      <c r="E23">
-        <v>0.5732335747706511</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24">
+      <c r="C23" s="4">
+        <v>0.57210642123915978</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0.60720629698987605</v>
+      </c>
+      <c r="E23" s="4">
+        <v>0.57323357477065107</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="3">
         <v>13</v>
       </c>
-      <c r="C24">
-        <v>0.5800840511003225</v>
-      </c>
-      <c r="D24">
+      <c r="C24" s="4">
+        <v>0.58008405110032246</v>
+      </c>
+      <c r="D24" s="4">
         <v>0.6153741822877431</v>
       </c>
-      <c r="E24">
-        <v>0.5810766731975729</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="E24" s="4">
+        <v>0.58107667319757295</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B25">
         <v>21</v>
       </c>
-      <c r="C25">
-        <v>0.6209265919882491</v>
-      </c>
-      <c r="D25">
-        <v>0.6487608906940898</v>
-      </c>
-      <c r="E25">
+      <c r="C25" s="2">
+        <v>0.62092659198824907</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0.64876089069408982</v>
+      </c>
+      <c r="E25" s="2">
         <v>0.6224788208273736</v>
       </c>
     </row>
